--- a/BOM/PDU_Control_Board_VER1.0.xlsx
+++ b/BOM/PDU_Control_Board_VER1.0.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\PDU_Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B3BC33-E1C0-4A2D-8246-2D173497AA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD32DB3-9F5D-4A27-8347-D0D31849629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="153">
   <si>
     <t>Reference</t>
   </si>
@@ -199,9 +199,6 @@
     <t>PESD2CAN</t>
   </si>
   <si>
-    <t>Dual Line CAN Bus Protector, 24Vrwm</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:SOT-23</t>
   </si>
   <si>
@@ -346,9 +343,6 @@
     <t>BSP75N</t>
   </si>
   <si>
-    <t>Self-Protected Low Side Driver with Temperature and Current Limit, SOT−223</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:SOT-223</t>
   </si>
   <si>
@@ -439,9 +433,6 @@
     <t>LMV321</t>
   </si>
   <si>
-    <t>Low-Voltage Rail-to-Rail Output Operational Amplifiers, SOT-23-5/SC-70-5</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:SOT-23-5</t>
   </si>
   <si>
@@ -467,25 +458,67 @@
   </si>
   <si>
     <t>Crystal:Crystal_SMD_SeikoEpson_FA238-4Pin_3.2x2.5mm</t>
+  </si>
+  <si>
+    <t>Resistor SMD</t>
+  </si>
+  <si>
+    <t>Inductor SMD</t>
+  </si>
+  <si>
+    <t>Operational Amplifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Side Driver </t>
+  </si>
+  <si>
+    <t>Dual Line CAN Bus Protector</t>
+  </si>
+  <si>
+    <t>Tantalum Capacitor</t>
+  </si>
+  <si>
+    <t>Capacitor SMD 50V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -515,9 +548,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -825,42 +864,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="27.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,7 +908,9 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
@@ -878,7 +919,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -887,7 +928,9 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="E3" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,7 +939,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -905,7 +948,9 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
@@ -914,7 +959,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -923,7 +968,9 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
@@ -932,7 +979,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -941,7 +988,9 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
@@ -950,7 +999,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -959,7 +1008,9 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
@@ -968,7 +1019,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -977,7 +1028,9 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
       </c>
@@ -986,7 +1039,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -995,7 +1048,9 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1004,7 +1059,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1015,7 +1070,9 @@
         <v>28</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1024,7 +1081,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1035,7 +1092,9 @@
         <v>31</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="E11" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1044,7 +1103,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -1053,7 +1112,9 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1062,7 +1123,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -1073,7 +1134,9 @@
         <v>36</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1082,7 +1145,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1093,7 +1156,9 @@
         <v>38</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1102,7 +1167,7 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -1113,7 +1178,9 @@
         <v>42</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1122,7 +1189,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -1133,7 +1200,9 @@
         <v>45</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="E16" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1142,7 +1211,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1151,7 +1220,9 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="E17" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1160,7 +1231,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1169,7 +1240,9 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="E18" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1178,7 +1251,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1187,7 +1260,9 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="E19" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
@@ -1196,7 +1271,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1218,7 +1293,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
@@ -1229,503 +1304,523 @@
         <v>58</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="G23" s="1">
         <v>5</v>
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" s="1">
         <v>5</v>
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="G25" s="1">
         <v>7</v>
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="1">
         <v>12</v>
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="G28" s="1">
         <v>3</v>
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="G30" s="1">
         <v>1</v>
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32" s="1">
         <v>13</v>
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G36" s="1">
         <v>5</v>
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F37" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G37" s="1">
         <v>18</v>
       </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G38" s="1">
         <v>11</v>
       </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B39" s="1">
         <v>120</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G39" s="1">
         <v>6</v>
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G41" s="1">
         <v>6</v>
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B42" s="1">
         <v>240</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B43" s="1">
         <v>49.9</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F43" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G43" s="1">
         <v>4</v>
       </c>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B44" s="1">
         <v>665</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F44" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F45" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -1734,156 +1829,166 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B46" s="1">
         <v>750</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F46" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G46" s="1">
         <v>2</v>
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
       </c>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G48" s="1">
         <v>5</v>
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B49" s="1">
         <v>100</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F49" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F50" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G50" s="1">
         <v>3</v>
       </c>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="1" t="s">
-        <v>139</v>
+      <c r="E51" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
